--- a/src/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-24.131095054909164</v>
+        <v>-24.124314637476605</v>
       </c>
       <c r="B1">
-        <v>14.4348836971876</v>
+        <v>14.446212623813402</v>
       </c>
       <c r="C1">
         <v>384.89451392788493</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-22.052056977639829</v>
+        <v>-22.177005427951858</v>
       </c>
       <c r="B2">
-        <v>14.697682580216405</v>
+        <v>14.519854319251163</v>
       </c>
       <c r="C2">
         <v>384.89451392788493</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-20.390354866083655</v>
+        <v>-20.565350014045453</v>
       </c>
       <c r="B3">
-        <v>14.364258544432122</v>
+        <v>14.114446475319815</v>
       </c>
       <c r="C3">
         <v>384.89451392788493</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-18.793400454899611</v>
+        <v>-19.007082307297313</v>
       </c>
       <c r="B4">
-        <v>13.938333343941512</v>
+        <v>13.632842989164228</v>
       </c>
       <c r="C4">
         <v>384.89451392788493</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-17.24157770279162</v>
+        <v>-17.486493035367666</v>
       </c>
       <c r="B5">
-        <v>13.447931243025559</v>
+        <v>13.097464342174554</v>
       </c>
       <c r="C5">
         <v>384.89451392788493</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-15.726879265032558</v>
+        <v>-15.997166463396185</v>
       </c>
       <c r="B6">
-        <v>12.904491855897703</v>
+        <v>12.517467156053497</v>
       </c>
       <c r="C6">
         <v>384.89451392788493</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-14.244728798407845</v>
+        <v>-14.535433947360554</v>
       </c>
       <c r="B7">
-        <v>12.314553130238091</v>
+        <v>11.898087368102951</v>
       </c>
       <c r="C7">
         <v>384.89451392788493</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-12.792429892138438</v>
+        <v>-13.09913202093993</v>
       </c>
       <c r="B8">
-        <v>11.68196726676052</v>
+        <v>11.242412706088748</v>
       </c>
       <c r="C8">
         <v>384.89451392788493</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-11.365777179049509</v>
+        <v>-11.684889731865207</v>
       </c>
       <c r="B9">
-        <v>11.012742221878161</v>
+        <v>10.555254237702759</v>
       </c>
       <c r="C9">
         <v>384.89451392788493</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-9.960232124452256</v>
+        <v>-10.289069651772865</v>
       </c>
       <c r="B10">
-        <v>10.313361928493041</v>
+        <v>9.8418033488455166</v>
       </c>
       <c r="C10">
         <v>384.89451392788493</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-8.5714324799977515</v>
+        <v>-8.9081759338700177</v>
       </c>
       <c r="B11">
-        <v>9.5900584697632514</v>
+        <v>9.10704935832615</v>
       </c>
       <c r="C11">
         <v>384.89451392788493</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.1970450631717329</v>
+        <v>-7.5403372978623695</v>
       </c>
       <c r="B12">
-        <v>8.8461651239180039</v>
+        <v>8.3536629821464263</v>
       </c>
       <c r="C12">
         <v>384.89451392788493</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-5.8426766684587133</v>
+        <v>-6.1900391478793484</v>
       </c>
       <c r="B13">
-        <v>8.0736717992149583</v>
+        <v>7.5752425921700572</v>
       </c>
       <c r="C13">
         <v>384.89451392788493</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-4.5116776475800737</v>
+        <v>-4.8599607516791741</v>
       </c>
       <c r="B14">
-        <v>7.2677920486510246</v>
+        <v>6.767964301993322</v>
       </c>
       <c r="C14">
         <v>384.89451392788493</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.190432604205871</v>
+        <v>-3.5392001471115551</v>
       </c>
       <c r="B15">
-        <v>6.4479773741516491</v>
+        <v>5.9473875362808268</v>
       </c>
       <c r="C15">
         <v>384.89451392788493</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.8664535818461425</v>
+        <v>-2.2177581267486848</v>
       </c>
       <c r="B16">
-        <v>5.6320685718143855</v>
+        <v>5.1277832962096266</v>
       </c>
       <c r="C16">
         <v>384.89451392788493</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.54872813142210031</v>
+        <v>-0.90282773196114485</v>
       </c>
       <c r="B17">
-        <v>4.8072256654965706</v>
+        <v>4.29888557793818</v>
       </c>
       <c r="C17">
         <v>384.89451392788493</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>0.75113532679333761</v>
+        <v>0.39629963617867303</v>
       </c>
       <c r="B18">
-        <v>3.9568643998582691</v>
+        <v>3.4474335708874793</v>
       </c>
       <c r="C18">
         <v>384.89451392788493</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>2.032520402531647</v>
+        <v>1.6791313865895954</v>
       </c>
       <c r="B19">
-        <v>3.0801041750106188</v>
+        <v>2.572724242547205</v>
       </c>
       <c r="C19">
         <v>384.89451392788493</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>3.297558713025408</v>
+        <v>2.9473746306882584</v>
       </c>
       <c r="B20">
-        <v>2.1799903049275189</v>
+        <v>1.6771940049242013</v>
       </c>
       <c r="C20">
         <v>384.89451392788493</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.5483818755071921</v>
+        <v>4.2027364798912883</v>
       </c>
       <c r="B21">
-        <v>1.2595681035828739</v>
+        <v>0.76327927002532125</v>
       </c>
       <c r="C21">
         <v>384.89451392788493</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.7867416969048868</v>
+        <v>5.4466197732120412</v>
       </c>
       <c r="B22">
-        <v>0.32134027269795212</v>
+        <v>-0.16701781174349772</v>
       </c>
       <c r="C22">
         <v>384.89451392788493</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.0128707429275936</v>
+        <v>6.6792102600507306</v>
       </c>
       <c r="B23">
-        <v>-0.63436093501649748</v>
+        <v>-1.1134321363799258</v>
       </c>
       <c r="C23">
         <v>384.89451392788493</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8.22662176897973</v>
+        <v>7.9003894174042957</v>
       </c>
       <c r="B24">
-        <v>-1.6077458791023607</v>
+        <v>-2.0761328614825456</v>
       </c>
       <c r="C24">
         <v>384.89451392788493</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>9.427847530465705</v>
+        <v>9.1100387222696746</v>
       </c>
       <c r="B25">
-        <v>-2.5990249191015247</v>
+        <v>-3.0552891446499397</v>
       </c>
       <c r="C25">
         <v>384.89451392788493</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>10.616337506422282</v>
+        <v>10.307988783056826</v>
       </c>
       <c r="B26">
-        <v>-3.60849881371557</v>
+        <v>-4.0511427438012415</v>
       </c>
       <c r="C26">
         <v>384.89451392788493</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>11.791628070415616</v>
+        <v>11.493866733827819</v>
       </c>
       <c r="B27">
-        <v>-4.6368299182848984</v>
+        <v>-5.0642258181378477</v>
       </c>
       <c r="C27">
         <v>384.89451392788493</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>12.953192319644209</v>
+        <v>12.667248840057727</v>
       </c>
       <c r="B28">
-        <v>-5.6847709873095953</v>
+        <v>-6.095143127181692</v>
       </c>
       <c r="C28">
         <v>384.89451392788493</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>14.100503351306562</v>
+        <v>13.827711367221639</v>
       </c>
       <c r="B29">
-        <v>-6.7530747752897557</v>
+        <v>-7.1444994304547205</v>
       </c>
       <c r="C29">
         <v>384.89451392788493</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>15.233315723418997</v>
+        <v>14.975055681008724</v>
       </c>
       <c r="B30">
-        <v>-7.8420919304990155</v>
+        <v>-8.2125782214741978</v>
       </c>
       <c r="C30">
         <v>384.89451392788493</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>16.352509837269132</v>
+        <v>16.109983547964532</v>
       </c>
       <c r="B31">
-        <v>-8.950564676305218</v>
+        <v>-9.2983779297386651</v>
       </c>
       <c r="C31">
         <v>384.89451392788493</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>17.45924755496242</v>
+        <v>17.23342183484872</v>
       </c>
       <c r="B32">
-        <v>-10.07683312984976</v>
+        <v>-10.40057571874201</v>
       </c>
       <c r="C32">
         <v>384.89451392788493</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>18.554690738604311</v>
+        <v>18.346297408420927</v>
       </c>
       <c r="B33">
-        <v>-11.219237408274037</v>
+        <v>-11.517848751978093</v>
       </c>
       <c r="C33">
         <v>384.89451392788493</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>19.639544128302603</v>
+        <v>19.4491709564795</v>
       </c>
       <c r="B34">
-        <v>-12.376770691561069</v>
+        <v>-12.649396808400608</v>
       </c>
       <c r="C34">
         <v>384.89451392788493</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>20.712683976174553</v>
+        <v>20.541138450977591</v>
       </c>
       <c r="B35">
-        <v>-13.551038411060445</v>
+        <v>-13.796510128802504</v>
       </c>
       <c r="C35">
         <v>384.89451392788493</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>21.772529412339761</v>
+        <v>21.620929684907068</v>
       </c>
       <c r="B36">
-        <v>-14.744299060963376</v>
+        <v>-14.961001569436544</v>
       </c>
       <c r="C36">
         <v>384.89451392788493</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>22.817499566917846</v>
+        <v>22.6872744512598</v>
       </c>
       <c r="B37">
-        <v>-15.958811135461094</v>
+        <v>-16.144683986555503</v>
       </c>
       <c r="C37">
         <v>384.89451392788493</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>23.844893921650417</v>
+        <v>23.738006002624985</v>
       </c>
       <c r="B38">
-        <v>-17.198432703377286</v>
+        <v>-17.350649790740224</v>
       </c>
       <c r="C38">
         <v>384.89451392788493</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>24.847533364767077</v>
+        <v>24.767371429981218</v>
       </c>
       <c r="B39">
-        <v>-18.473420132065574</v>
+        <v>-18.587109609883832</v>
       </c>
       <c r="C39">
         <v>384.89451392788493</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>25.81711913611943</v>
+        <v>25.768721283904419</v>
       </c>
       <c r="B40">
-        <v>-19.795629363512042</v>
+        <v>-19.863553626207541</v>
       </c>
       <c r="C40">
         <v>384.89451392788493</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>26.745352475559091</v>
+        <v>26.735406114970527</v>
       </c>
       <c r="B41">
-        <v>-21.176916339702792</v>
+        <v>-21.189472021932549</v>
       </c>
       <c r="C41">
         <v>384.89451392788493</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>26.745352475559091</v>
+        <v>26.735406114970527</v>
       </c>
       <c r="B42">
-        <v>-21.176916339702792</v>
+        <v>-21.189472021932549</v>
       </c>
       <c r="C42">
         <v>384.89451392788493</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>25.426379566329004</v>
+        <v>25.455919974827271</v>
       </c>
       <c r="B43">
-        <v>-20.353855603127208</v>
+        <v>-20.309987794340262</v>
       </c>
       <c r="C43">
         <v>384.89451392788493</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>24.133160656027055</v>
+        <v>24.195489962786286</v>
       </c>
       <c r="B44">
-        <v>-19.494001669526764</v>
+        <v>-19.403306408519104</v>
       </c>
       <c r="C44">
         <v>384.89451392788493</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>22.857456830013192</v>
+        <v>22.947526515069839</v>
       </c>
       <c r="B45">
-        <v>-18.60912498319124</v>
+        <v>-18.478832577103258</v>
       </c>
       <c r="C45">
         <v>384.89451392788493</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>21.591029173647339</v>
+        <v>21.705440067900206</v>
       </c>
       <c r="B46">
-        <v>-17.710995988410421</v>
+        <v>-17.545971012726927</v>
       </c>
       <c r="C46">
         <v>384.89451392788493</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>20.326756212674432</v>
+        <v>20.463535388428397</v>
       </c>
       <c r="B47">
-        <v>-16.809788709269096</v>
+        <v>-16.612850027086626</v>
       </c>
       <c r="C47">
         <v>384.89451392788493</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>19.061986234379294</v>
+        <v>19.21969456752042</v>
       </c>
       <c r="B48">
-        <v>-15.90929148903213</v>
+        <v>-15.682492328128204</v>
       </c>
       <c r="C48">
         <v>384.89451392788493</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>17.79518496643173</v>
+        <v>17.972694026971009</v>
       </c>
       <c r="B49">
-        <v>-15.011696250759384</v>
+        <v>-14.75664422285983</v>
       </c>
       <c r="C49">
         <v>384.89451392788493</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>16.524818136501558</v>
+        <v>16.721310188574911</v>
       </c>
       <c r="B50">
-        <v>-14.119194917510725</v>
+        <v>-13.837052018289683</v>
       </c>
       <c r="C50">
         <v>384.89451392788493</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>15.249806234917406</v>
+        <v>15.464683292166958</v>
       </c>
       <c r="B51">
-        <v>-13.233329720150568</v>
+        <v>-12.924942775504126</v>
       </c>
       <c r="C51">
         <v>384.89451392788493</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>13.970888802643184</v>
+        <v>14.203408849742315</v>
       </c>
       <c r="B52">
-        <v>-12.353044120761483</v>
+        <v>-12.019466571902269</v>
       </c>
       <c r="C52">
         <v>384.89451392788493</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>12.689260143301624</v>
+        <v>12.938446191336226</v>
       </c>
       <c r="B53">
-        <v>-11.476631889230585</v>
+        <v>-11.119254238961414</v>
       </c>
       <c r="C53">
         <v>384.89451392788493</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>11.406114560515436</v>
+        <v>11.670754646983927</v>
       </c>
       <c r="B54">
-        <v>-10.602386795444982</v>
+        <v>-10.222936608158841</v>
       </c>
       <c r="C54">
         <v>384.89451392788493</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>10.122362703966875</v>
+        <v>10.401066251913004</v>
       </c>
       <c r="B55">
-        <v>-9.7290078487013254</v>
+        <v>-9.32946890912952</v>
       </c>
       <c r="C55">
         <v>384.89451392788493</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.8377806075762759</v>
+        <v>9.1292038621203986</v>
       </c>
       <c r="B56">
-        <v>-8.8568150159344317</v>
+        <v>-8.4391039641390631</v>
       </c>
       <c r="C56">
         <v>384.89451392788493</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>7.5518606513234854</v>
+        <v>7.8547630387953777</v>
       </c>
       <c r="B57">
-        <v>-7.9865335034886451</v>
+        <v>-7.55241899361075</v>
       </c>
       <c r="C57">
         <v>384.89451392788493</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6.2640952151883642</v>
+        <v>6.57733934312722</v>
       </c>
       <c r="B58">
-        <v>-7.1188885177083234</v>
+        <v>-6.6699912179678611</v>
       </c>
       <c r="C58">
         <v>384.89451392788493</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.9740378215335861</v>
+        <v>5.2965770694760987</v>
       </c>
       <c r="B59">
-        <v>-6.2545179144745058</v>
+        <v>-5.792328305007179</v>
       </c>
       <c r="C59">
         <v>384.89451392788493</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.6814865622531809</v>
+        <v>4.0123154448858331</v>
       </c>
       <c r="B60">
-        <v>-5.3937101478150495</v>
+        <v>-4.9196597120195511</v>
       </c>
       <c r="C60">
         <v>384.89451392788493</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.3863006716240074</v>
+        <v>2.724442429571142</v>
       </c>
       <c r="B61">
-        <v>-4.536666321294506</v>
+        <v>-4.052145343669336</v>
       </c>
       <c r="C61">
         <v>384.89451392788493</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.0883393839229214</v>
+        <v>1.4328459837467473</v>
       </c>
       <c r="B62">
-        <v>-3.683587538477421</v>
+        <v>-3.1899451046208886</v>
       </c>
       <c r="C62">
         <v>384.89451392788493</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.21216045849583209</v>
+        <v>0.13771613632632432</v>
       </c>
       <c r="B63">
-        <v>-2.834135436866096</v>
+        <v>-2.3327877830936612</v>
       </c>
       <c r="C63">
         <v>384.89451392788493</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.5134515809685134</v>
+        <v>-1.1595488089806809</v>
       </c>
       <c r="B64">
-        <v>-1.9858137897137882</v>
+        <v>-1.4786777015274439</v>
       </c>
       <c r="C64">
         <v>384.89451392788493</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.8134091007539892</v>
+        <v>-2.4572484797658611</v>
       </c>
       <c r="B65">
-        <v>-1.1355869042115072</v>
+        <v>-0.62518806591712661</v>
       </c>
       <c r="C65">
         <v>384.89451392788493</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.1099081351111391</v>
+        <v>-3.7536825036208215</v>
       </c>
       <c r="B66">
-        <v>-0.28041908755025485</v>
+        <v>0.230107917742409</v>
       </c>
       <c r="C66">
         <v>384.89451392788493</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-5.403573587207803</v>
+        <v>-5.0493519902355972</v>
       </c>
       <c r="B67">
-        <v>0.57879689851129612</v>
+        <v>1.0864950590695228</v>
       </c>
       <c r="C67">
         <v>384.89451392788493</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-6.7060295038476907</v>
+        <v>-6.3535639776939874</v>
       </c>
       <c r="B68">
-        <v>1.4254544739438231</v>
+        <v>1.9306902301355633</v>
       </c>
       <c r="C68">
         <v>384.89451392788493</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-8.0262816405542416</v>
+        <v>-7.6735297241785121</v>
       </c>
       <c r="B69">
-        <v>2.2466876547789365</v>
+        <v>2.7524014278239228</v>
       </c>
       <c r="C69">
         <v>384.89451392788493</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-9.3518634440938921</v>
+        <v>-8.9992714398727944</v>
       </c>
       <c r="B70">
-        <v>3.060306659562618</v>
+        <v>3.5658690858131448</v>
       </c>
       <c r="C70">
         <v>384.89451392788493</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-10.669182899237477</v>
+        <v>-10.319910559408873</v>
       </c>
       <c r="B71">
-        <v>3.8857295870409008</v>
+        <v>4.3866192365704624</v>
       </c>
       <c r="C71">
         <v>384.89451392788493</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-11.981618451530377</v>
+        <v>-11.638154463211325</v>
       </c>
       <c r="B72">
-        <v>4.7181298542456114</v>
+        <v>5.21078787092268</v>
       </c>
       <c r="C72">
         <v>384.89451392788493</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-13.294807273197396</v>
+        <v>-12.958518953524013</v>
       </c>
       <c r="B73">
-        <v>5.549453970574791</v>
+        <v>6.0319299761422416</v>
       </c>
       <c r="C73">
         <v>384.89451392788493</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-14.606450982406535</v>
+        <v>-14.279167574075512</v>
       </c>
       <c r="B74">
-        <v>6.3829854966055493</v>
+        <v>6.8526665669246078</v>
       </c>
       <c r="C74">
         <v>384.89451392788493</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-15.912224381237925</v>
+        <v>-15.596641553351498</v>
       </c>
       <c r="B75">
-        <v>7.2249035837652391</v>
+        <v>7.6779340477506759</v>
       </c>
       <c r="C75">
         <v>384.89451392788493</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-17.207630561477128</v>
+        <v>-16.907345117381404</v>
       </c>
       <c r="B76">
-        <v>8.08163269570313</v>
+        <v>8.51286435482007</v>
       </c>
       <c r="C76">
         <v>384.89451392788493</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-18.488508147631766</v>
+        <v>-18.207951335083511</v>
       </c>
       <c r="B77">
-        <v>8.9591179405483512</v>
+        <v>9.3622057282034064</v>
       </c>
       <c r="C77">
         <v>384.89451392788493</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-19.752209605392391</v>
+        <v>-19.496345649387735</v>
       </c>
       <c r="B78">
-        <v>9.8611416921275481</v>
+        <v>10.228976091736536</v>
       </c>
       <c r="C78">
         <v>384.89451392788493</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-20.994209697179439</v>
+        <v>-20.768910556182995</v>
       </c>
       <c r="B79">
-        <v>10.794168886558573</v>
+        <v>11.118338395163242</v>
       </c>
       <c r="C79">
         <v>384.89451392788493</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-22.206556667965067</v>
+        <v>-22.019285947591886</v>
       </c>
       <c r="B80">
-        <v>11.769559720378242</v>
+        <v>12.039369868619971</v>
       </c>
       <c r="C80">
         <v>384.89451392788493</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-23.369693579004775</v>
+        <v>-23.231821693465939</v>
       </c>
       <c r="B81">
-        <v>12.81525402158908</v>
+        <v>13.014406584978728</v>
       </c>
       <c r="C81">
         <v>384.89451392788493</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-24.131095054909164</v>
+        <v>-24.124314637476605</v>
       </c>
       <c r="B82">
-        <v>14.4348836971876</v>
+        <v>14.446212623813402</v>
       </c>
       <c r="C82">
         <v>384.89451392788493</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-29.873481190069089</v>
+        <v>-29.874048934407366</v>
       </c>
       <c r="B1">
-        <v>12.974861416235079</v>
+        <v>12.973554156381027</v>
       </c>
       <c r="C1">
         <v>452.5754307907855</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-27.954391394892475</v>
+        <v>-28.012336962130895</v>
       </c>
       <c r="B2">
-        <v>12.813258015163648</v>
+        <v>12.691684473520814</v>
       </c>
       <c r="C2">
         <v>452.5754307907855</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-26.181262796116798</v>
+        <v>-26.260901102045281</v>
       </c>
       <c r="B3">
-        <v>12.345572496643388</v>
+        <v>12.178538610278361</v>
       </c>
       <c r="C3">
         <v>452.5754307907855</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-24.431246273074187</v>
+        <v>-24.527612179062743</v>
       </c>
       <c r="B4">
-        <v>11.829420719600671</v>
+        <v>11.627334148347082</v>
       </c>
       <c r="C4">
         <v>452.5754307907855</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-22.697514067111271</v>
+        <v>-22.807349098430866</v>
       </c>
       <c r="B5">
-        <v>11.279120563565044</v>
+        <v>11.048811285310878</v>
       </c>
       <c r="C5">
         <v>452.5754307907855</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-20.977282941547315</v>
+        <v>-21.0980239196955</v>
       </c>
       <c r="B6">
-        <v>10.700508504241009</v>
+        <v>10.447348946791131</v>
       </c>
       <c r="C6">
         <v>452.5754307907855</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-19.26896460046116</v>
+        <v>-19.398444879092072</v>
       </c>
       <c r="B7">
-        <v>10.09691521437362</v>
+        <v>9.8254465550644952</v>
       </c>
       <c r="C7">
         <v>452.5754307907855</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-17.571625516361244</v>
+        <v>-17.707911270979071</v>
       </c>
       <c r="B8">
-        <v>9.4702983106333214</v>
+        <v>9.1845736625219416</v>
       </c>
       <c r="C8">
         <v>452.5754307907855</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-15.88380576289693</v>
+        <v>-16.025327686167884</v>
       </c>
       <c r="B9">
-        <v>8.8237192734665673</v>
+        <v>8.5270276121516027</v>
       </c>
       <c r="C9">
         <v>452.5754307907855</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-14.203929028019674</v>
+        <v>-14.349511463270401</v>
       </c>
       <c r="B10">
-        <v>8.1604836453153</v>
+        <v>7.8552887363037369</v>
       </c>
       <c r="C10">
         <v>452.5754307907855</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-12.530479855748359</v>
+        <v>-12.679325635647714</v>
       </c>
       <c r="B11">
-        <v>7.4837693528273972</v>
+        <v>7.1717415341798771</v>
       </c>
       <c r="C11">
         <v>452.5754307907855</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-10.862649524719139</v>
+        <v>-11.014163267168581</v>
       </c>
       <c r="B12">
-        <v>6.7952722929506431</v>
+        <v>6.4776589004022691</v>
       </c>
       <c r="C12">
         <v>452.5754307907855</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-9.2023953959698019</v>
+        <v>-9.35549184898318</v>
       </c>
       <c r="B13">
-        <v>6.0908878596265206</v>
+        <v>5.7699631444247546</v>
       </c>
       <c r="C13">
         <v>452.5754307907855</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-7.55088830729023</v>
+        <v>-7.7041890630306558</v>
       </c>
       <c r="B14">
-        <v>5.3681607940687694</v>
+        <v>5.0468135509514855</v>
       </c>
       <c r="C14">
         <v>452.5754307907855</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-5.9033869210770735</v>
+        <v>-6.0566989271246161</v>
       </c>
       <c r="B15">
-        <v>4.6370337295864905</v>
+        <v>4.3156678908562887</v>
       </c>
       <c r="C15">
         <v>452.5754307907855</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-4.2555425055046134</v>
+        <v>-4.4097599118441844</v>
       </c>
       <c r="B16">
-        <v>3.9066260011690908</v>
+        <v>3.5833663950076597</v>
       </c>
       <c r="C16">
         <v>452.5754307907855</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.6104889272508465</v>
+        <v>-2.7657219629560443</v>
       </c>
       <c r="B17">
-        <v>3.1703658584318122</v>
+        <v>2.8449806480831068</v>
       </c>
       <c r="C17">
         <v>452.5754307907855</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.97227296190087931</v>
+        <v>-1.1276196786837016</v>
       </c>
       <c r="B18">
-        <v>2.4197671717013662</v>
+        <v>2.09414634985312</v>
       </c>
       <c r="C18">
         <v>452.5754307907855</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.65888957783554369</v>
+        <v>0.50438520810967846</v>
       </c>
       <c r="B19">
-        <v>1.6543773795244516</v>
+        <v>1.33052430665109</v>
       </c>
       <c r="C19">
         <v>452.5754307907855</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.2837406199675359</v>
+        <v>2.1308491809010324</v>
       </c>
       <c r="B20">
-        <v>0.87575231250275432</v>
+        <v>0.55528160145112082</v>
       </c>
       <c r="C20">
         <v>452.5754307907855</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.9030220925041865</v>
+        <v>3.7523287231672735</v>
       </c>
       <c r="B21">
-        <v>0.085447801237973756</v>
+        <v>-0.23041468277266974</v>
       </c>
       <c r="C21">
         <v>452.5754307907855</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.5173438490362328</v>
+        <v>5.369281242702785</v>
       </c>
       <c r="B22">
-        <v>-0.71525728507050945</v>
+        <v>-1.0256052491657157</v>
       </c>
       <c r="C22">
         <v>452.5754307907855</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.1267874454808862</v>
+        <v>6.9817678445717135</v>
       </c>
       <c r="B23">
-        <v>-1.5261919228325294</v>
+        <v>-1.8301619453516</v>
       </c>
       <c r="C23">
         <v>452.5754307907855</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8.7313023633369848</v>
+        <v>8.5897505581556484</v>
       </c>
       <c r="B24">
-        <v>-2.3474620498602259</v>
+        <v>-2.6441644050734405</v>
       </c>
       <c r="C24">
         <v>452.5754307907855</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>10.330838084103384</v>
+        <v>10.193191412836201</v>
       </c>
       <c r="B25">
-        <v>-3.1791736039657512</v>
+        <v>-3.4676922620743689</v>
       </c>
       <c r="C25">
         <v>452.5754307907855</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>11.925322301298184</v>
+        <v>11.792036070621924</v>
       </c>
       <c r="B26">
-        <v>-4.0214782125790336</v>
+        <v>-4.3008594765118353</v>
       </c>
       <c r="C26">
         <v>452.5754307907855</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>13.514595556516598</v>
+        <v>13.386164724029255</v>
       </c>
       <c r="B27">
-        <v>-4.8747102616011961</v>
+        <v>-5.1439173142006407</v>
       </c>
       <c r="C27">
         <v>452.5754307907855</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>15.098476603373083</v>
+        <v>14.975441198201573</v>
       </c>
       <c r="B28">
-        <v>-5.7392498265511422</v>
+        <v>-5.9971513673699093</v>
       </c>
       <c r="C28">
         <v>452.5754307907855</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>16.676784195482128</v>
+        <v>16.559729318282283</v>
       </c>
       <c r="B29">
-        <v>-6.6154769829477837</v>
+        <v>-6.8608472282487751</v>
       </c>
       <c r="C29">
         <v>452.5754307907855</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>18.24943542903377</v>
+        <v>18.138966631438187</v>
       </c>
       <c r="B30">
-        <v>-7.5035655809260806</v>
+        <v>-7.7351358758174324</v>
       </c>
       <c r="C30">
         <v>452.5754307907855</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>19.816740770520379</v>
+        <v>19.713385572929752</v>
       </c>
       <c r="B31">
-        <v>-8.402864569085196</v>
+        <v>-8.6195298360603267</v>
       </c>
       <c r="C31">
         <v>452.5754307907855</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>21.379109029009943</v>
+        <v>21.283292300040888</v>
       </c>
       <c r="B32">
-        <v>-9.31251667064036</v>
+        <v>-9.5133870217129868</v>
       </c>
       <c r="C32">
         <v>452.5754307907855</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>22.936949013570405</v>
+        <v>22.84899297005547</v>
       </c>
       <c r="B33">
-        <v>-10.231664608806785</v>
+        <v>-10.41606534551093</v>
       </c>
       <c r="C33">
         <v>452.5754307907855</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>24.490510546312667</v>
+        <v>24.410674481725241</v>
       </c>
       <c r="B34">
-        <v>-11.159784504070078</v>
+        <v>-11.327172834718052</v>
       </c>
       <c r="C34">
         <v>452.5754307907855</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>26.039407501519413</v>
+        <v>25.968046699673383</v>
       </c>
       <c r="B35">
-        <v>-12.097686065997387</v>
+        <v>-12.247317974711766</v>
       </c>
       <c r="C35">
         <v>452.5754307907855</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>27.583094766516258</v>
+        <v>27.520700229990918</v>
       </c>
       <c r="B36">
-        <v>-13.046512401426236</v>
+        <v>-13.177359365397866</v>
       </c>
       <c r="C36">
         <v>452.5754307907855</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>29.121027228628858</v>
+        <v>29.068225678768883</v>
       </c>
       <c r="B37">
-        <v>-14.007406617194175</v>
+        <v>-14.118155606682155</v>
       </c>
       <c r="C37">
         <v>452.5754307907855</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>30.652269920953124</v>
+        <v>30.609921261947097</v>
       </c>
       <c r="B38">
-        <v>-14.98232934843435</v>
+        <v>-15.07117851266532</v>
       </c>
       <c r="C38">
         <v>452.5754307907855</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>32.174328459666228</v>
+        <v>32.143915634860527</v>
       </c>
       <c r="B39">
-        <v>-15.9765113434624</v>
+        <v>-16.040352754227634</v>
       </c>
       <c r="C39">
         <v>452.5754307907855</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>33.684318606715649</v>
+        <v>33.668045062692947</v>
       </c>
       <c r="B40">
-        <v>-16.996000878889589</v>
+        <v>-17.03021621644427</v>
       </c>
       <c r="C40">
         <v>452.5754307907855</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>35.179356124048844</v>
+        <v>35.180145810628112</v>
       </c>
       <c r="B41">
-        <v>-18.046846231327166</v>
+        <v>-18.045306784390391</v>
       </c>
       <c r="C41">
         <v>452.5754307907855</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>35.179356124048844</v>
+        <v>35.180145810628112</v>
       </c>
       <c r="B42">
-        <v>-18.046846231327166</v>
+        <v>-18.045306784390391</v>
       </c>
       <c r="C42">
         <v>452.5754307907855</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>33.548168132009884</v>
+        <v>33.565941577049166</v>
       </c>
       <c r="B43">
-        <v>-17.281509812888249</v>
+        <v>-17.244352385141774</v>
       </c>
       <c r="C43">
         <v>452.5754307907855</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>31.925410277502188</v>
+        <v>31.957244129718969</v>
       </c>
       <c r="B44">
-        <v>-16.498495310070879</v>
+        <v>-16.431848898203253</v>
       </c>
       <c r="C44">
         <v>452.5754307907855</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>30.308204361274619</v>
+        <v>30.351895772068524</v>
       </c>
       <c r="B45">
-        <v>-15.703838336058231</v>
+        <v>-15.612321544957675</v>
       </c>
       <c r="C45">
         <v>452.5754307907855</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>28.693672184076039</v>
+        <v>28.747738807528833</v>
       </c>
       <c r="B46">
-        <v>-14.903574504033463</v>
+        <v>-14.790295546787862</v>
       </c>
       <c r="C46">
         <v>452.5754307907855</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>27.079325190384328</v>
+        <v>27.142907719200757</v>
       </c>
       <c r="B47">
-        <v>-14.102922340306179</v>
+        <v>-13.969683352313027</v>
       </c>
       <c r="C47">
         <v>452.5754307907855</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>25.464233399593446</v>
+        <v>25.536705708864567</v>
       </c>
       <c r="B48">
-        <v>-13.303832023691754</v>
+        <v>-13.151946319097888</v>
       </c>
       <c r="C48">
         <v>452.5754307907855</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>23.847856474826344</v>
+        <v>23.928728157970362</v>
       </c>
       <c r="B49">
-        <v>-12.507436646131982</v>
+        <v>-12.337933031943527</v>
       </c>
       <c r="C49">
         <v>452.5754307907855</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>22.229654079205986</v>
+        <v>22.318570447968277</v>
       </c>
       <c r="B50">
-        <v>-11.714869299568672</v>
+        <v>-11.528492075651037</v>
       </c>
       <c r="C50">
         <v>452.5754307907855</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>20.609244628739482</v>
+        <v>20.705946984789122</v>
       </c>
       <c r="B51">
-        <v>-10.926930169526543</v>
+        <v>-10.724222411356667</v>
       </c>
       <c r="C51">
         <v>452.5754307907855</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>18.986881550970498</v>
+        <v>19.09104827228656</v>
       </c>
       <c r="B52">
-        <v>-10.143087815861929</v>
+        <v>-9.9247245055372844</v>
       </c>
       <c r="C52">
         <v>452.5754307907855</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>17.362977026326849</v>
+        <v>17.474183838794957</v>
       </c>
       <c r="B53">
-        <v>-9.3624778920140859</v>
+        <v>-9.1293492010049224</v>
       </c>
       <c r="C53">
         <v>452.5754307907855</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>15.737943235236303</v>
+        <v>15.855663212648654</v>
       </c>
       <c r="B54">
-        <v>-8.5842360514222484</v>
+        <v>-8.33744734057159</v>
       </c>
       <c r="C54">
         <v>452.5754307907855</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>14.112093790410716</v>
+        <v>14.235721975038878</v>
       </c>
       <c r="B55">
-        <v>-7.8077046450313015</v>
+        <v>-7.5485248524297877</v>
       </c>
       <c r="C55">
         <v>452.5754307907855</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>12.485348033698068</v>
+        <v>12.614299918584296</v>
       </c>
       <c r="B56">
-        <v>-7.0330528138086379</v>
+        <v>-6.7627080062938791</v>
       </c>
       <c r="C56">
         <v>452.5754307907855</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>10.857526739230361</v>
+        <v>10.991262888760412</v>
       </c>
       <c r="B57">
-        <v>-6.2606563962272768</v>
+        <v>-5.98027815725869</v>
       </c>
       <c r="C57">
         <v>452.5754307907855</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>9.228450681139611</v>
+        <v>9.3664767310427628</v>
       </c>
       <c r="B58">
-        <v>-5.4908912307602451</v>
+        <v>-5.2015166604190535</v>
       </c>
       <c r="C58">
         <v>452.5754307907855</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>7.5979621984219312</v>
+        <v>7.7398234351837392</v>
       </c>
       <c r="B59">
-        <v>-4.7240879341405924</v>
+        <v>-4.4266710123430508</v>
       </c>
       <c r="C59">
         <v>452.5754307907855</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5.9659898895298848</v>
+        <v>6.11124956804332</v>
       </c>
       <c r="B60">
-        <v>-3.9603962361415088</v>
+        <v>-3.6558532754917961</v>
       </c>
       <c r="C60">
         <v>452.5754307907855</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4.3324839177801273</v>
+        <v>4.4807178407583423</v>
       </c>
       <c r="B61">
-        <v>-3.1999206447962063</v>
+        <v>-2.8891416537996446</v>
       </c>
       <c r="C61">
         <v>452.5754307907855</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.6973944464893274</v>
+        <v>2.8481909644656684</v>
       </c>
       <c r="B62">
-        <v>-2.4427656681379055</v>
+        <v>-2.1266143512009634</v>
       </c>
       <c r="C62">
         <v>452.5754307907855</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.0608034817022449</v>
+        <v>1.2137304943156819</v>
       </c>
       <c r="B63">
-        <v>-1.6887593386544175</v>
+        <v>-1.3681422713776139</v>
       </c>
       <c r="C63">
         <v>452.5754307907855</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.57667959962402693</v>
+        <v>-0.42220663848713852</v>
       </c>
       <c r="B64">
-        <v>-0.93662378665191037</v>
+        <v>-0.612767117001434</v>
       </c>
       <c r="C64">
         <v>452.5754307907855</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2143135778042815</v>
+        <v>-2.0590646587247634</v>
       </c>
       <c r="B65">
-        <v>-0.18480466689115363</v>
+        <v>0.14067670950822958</v>
       </c>
       <c r="C65">
         <v>452.5754307907855</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.8513572331533368</v>
+        <v>-3.6962877911791869</v>
       </c>
       <c r="B66">
-        <v>0.56825236586709482</v>
+        <v>0.89335480573204262</v>
       </c>
       <c r="C66">
         <v>452.5754307907855</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-5.4880272729918627</v>
+        <v>-5.3340386632424064</v>
       </c>
       <c r="B67">
-        <v>1.3220928741612685</v>
+        <v>1.644926101955984</v>
       </c>
       <c r="C67">
         <v>452.5754307907855</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-7.1283721126640121</v>
+        <v>-6.9753535127465023</v>
       </c>
       <c r="B68">
-        <v>2.0682272897266025</v>
+        <v>2.3890228592873175</v>
       </c>
       <c r="C68">
         <v>452.5754307907855</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-8.77552752748192</v>
+        <v>-8.6225841939171524</v>
       </c>
       <c r="B69">
-        <v>2.8000798597531311</v>
+        <v>3.1207126598948234</v>
       </c>
       <c r="C69">
         <v>452.5754307907855</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-10.425147024606117</v>
+        <v>-10.272471416114264</v>
       </c>
       <c r="B70">
-        <v>3.5267652240532481</v>
+        <v>3.8468310393720162</v>
       </c>
       <c r="C70">
         <v>452.5754307907855</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-12.072491709061318</v>
+        <v>-11.921461639555364</v>
       </c>
       <c r="B71">
-        <v>4.2582208937200932</v>
+        <v>4.5748306462698736</v>
       </c>
       <c r="C71">
         <v>452.5754307907855</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-13.718735345480583</v>
+        <v>-13.570435472754197</v>
       </c>
       <c r="B72">
-        <v>4.9919854723474231</v>
+        <v>5.3028646275444977</v>
       </c>
       <c r="C72">
         <v>452.5754307907855</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-15.36583845451359</v>
+        <v>-15.220863566182885</v>
       </c>
       <c r="B73">
-        <v>5.7239477281383371</v>
+        <v>6.0278486667730862</v>
       </c>
       <c r="C73">
         <v>452.5754307907855</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-17.012995921268196</v>
+        <v>-16.872142589850945</v>
       </c>
       <c r="B74">
-        <v>6.4557959952326742</v>
+        <v>6.751048095612135</v>
       </c>
       <c r="C74">
         <v>452.5754307907855</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-18.658696121734341</v>
+        <v>-18.523139408738874</v>
       </c>
       <c r="B75">
-        <v>7.1907001645959685</v>
+        <v>7.4748393774131507</v>
       </c>
       <c r="C75">
         <v>452.5754307907855</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-20.301367030972031</v>
+        <v>-20.172675648173723</v>
       </c>
       <c r="B76">
-        <v>7.931956788559777</v>
+        <v>8.2016938542284112</v>
       </c>
       <c r="C76">
         <v>452.5754307907855</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-21.939553242271348</v>
+        <v>-21.819660418192836</v>
       </c>
       <c r="B77">
-        <v>8.6826178698378769</v>
+        <v>8.9338993911156148</v>
       </c>
       <c r="C77">
         <v>452.5754307907855</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-23.572326222772528</v>
+        <v>-23.46339800732818</v>
       </c>
       <c r="B78">
-        <v>9.4446305513069166</v>
+        <v>9.6729150664533776</v>
       </c>
       <c r="C78">
         <v>452.5754307907855</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-25.198102886121927</v>
+        <v>-25.102701860904645</v>
       </c>
       <c r="B79">
-        <v>10.221314581195676</v>
+        <v>10.421229377774123</v>
       </c>
       <c r="C79">
         <v>452.5754307907855</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-26.814105632127067</v>
+        <v>-26.735489674439087</v>
       </c>
       <c r="B80">
-        <v>11.018494615435383</v>
+        <v>11.183209430679318</v>
       </c>
       <c r="C80">
         <v>452.5754307907855</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-28.413512668076393</v>
+        <v>-28.356646318573453</v>
       </c>
       <c r="B81">
-        <v>11.850476022914702</v>
+        <v>11.969582911850921</v>
       </c>
       <c r="C81">
         <v>452.5754307907855</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-29.873481190069089</v>
+        <v>-29.874048934407366</v>
       </c>
       <c r="B82">
-        <v>12.974861416235079</v>
+        <v>12.973554156381027</v>
       </c>
       <c r="C82">
         <v>452.5754307907855</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-34.3486098284991</v>
+        <v>-34.352103723059315</v>
       </c>
       <c r="B1">
-        <v>12.254042935744762</v>
+        <v>12.244244983734808</v>
       </c>
       <c r="C1">
         <v>511.37584442281513</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-32.268024045745882</v>
+        <v>-32.324553100345106</v>
       </c>
       <c r="B2">
-        <v>12.046504506289413</v>
+        <v>11.897701505082448</v>
       </c>
       <c r="C2">
         <v>511.37584442281513</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-30.288320936908505</v>
+        <v>-30.364805006581715</v>
       </c>
       <c r="B3">
-        <v>11.573947077908704</v>
+        <v>11.372887718334653</v>
       </c>
       <c r="C3">
         <v>511.37584442281513</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-28.324198128689403</v>
+        <v>-28.416033601142207</v>
       </c>
       <c r="B4">
-        <v>11.060460166668944</v>
+        <v>10.819213391432308</v>
       </c>
       <c r="C4">
         <v>511.37584442281513</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-26.370916049170912</v>
+        <v>-26.475081342114745</v>
       </c>
       <c r="B5">
-        <v>10.518494638077572</v>
+        <v>10.244980515144146</v>
       </c>
       <c r="C5">
         <v>511.37584442281513</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-24.426543478217269</v>
+        <v>-24.54066152974227</v>
       </c>
       <c r="B6">
-        <v>9.9531238115383562</v>
+        <v>9.6535721544629443</v>
       </c>
       <c r="C6">
         <v>511.37584442281513</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-22.489978831571808</v>
+        <v>-22.612040154176508</v>
       </c>
       <c r="B7">
-        <v>9.36724155123635</v>
+        <v>9.0469182102909862</v>
       </c>
       <c r="C7">
         <v>511.37584442281513</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-20.560575129212413</v>
+        <v>-20.688786054910562</v>
       </c>
       <c r="B8">
-        <v>8.7625474750655687</v>
+        <v>8.426152314626842</v>
       </c>
       <c r="C8">
         <v>511.37584442281513</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-18.637319751724537</v>
+        <v>-18.770224509910552</v>
       </c>
       <c r="B9">
-        <v>8.1417017363815862</v>
+        <v>7.7930484854418216</v>
       </c>
       <c r="C9">
         <v>511.37584442281513</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-16.719119205778963</v>
+        <v>-16.855626929161037</v>
       </c>
       <c r="B10">
-        <v>7.5075769444857983</v>
+        <v>7.1495223735020037</v>
       </c>
       <c r="C10">
         <v>511.37584442281513</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-14.804922141780278</v>
+        <v>-14.944292812247369</v>
       </c>
       <c r="B11">
-        <v>6.8629349970012923</v>
+        <v>6.4974157747798138</v>
       </c>
       <c r="C11">
         <v>511.37584442281513</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-12.894167896177748</v>
+        <v>-13.035848545013003</v>
       </c>
       <c r="B12">
-        <v>6.2092487582681812</v>
+        <v>5.8377110171002684</v>
       </c>
       <c r="C12">
         <v>511.37584442281513</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-10.988216405865666</v>
+        <v>-11.131199968733087</v>
       </c>
       <c r="B13">
-        <v>5.542945671172987</v>
+        <v>5.1680264104924314</v>
       </c>
       <c r="C13">
         <v>511.37584442281513</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-9.0878814039637632</v>
+        <v>-9.2308890693248831</v>
       </c>
       <c r="B14">
-        <v>4.8618880570796019</v>
+        <v>4.486936934415807</v>
       </c>
       <c r="C14">
         <v>511.37584442281513</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-7.1898712080485385</v>
+        <v>-7.3327229558423808</v>
       </c>
       <c r="B15">
-        <v>4.1747231727150078</v>
+        <v>3.8002082638476091</v>
       </c>
       <c r="C15">
         <v>511.37584442281513</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-5.2911667025817968</v>
+        <v>-5.434690319114706</v>
       </c>
       <c r="B16">
-        <v>3.4893822410188604</v>
+        <v>3.1131286485200618</v>
       </c>
       <c r="C16">
         <v>511.37584442281513</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.3939444551097027</v>
+        <v>-3.5382410539347102</v>
       </c>
       <c r="B17">
-        <v>2.8001474144184217</v>
+        <v>2.4218859416677123</v>
       </c>
       <c r="C17">
         <v>511.37584442281513</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.5010148718948515</v>
+        <v>-1.6452473064420761</v>
       </c>
       <c r="B18">
-        <v>2.0996357496849449</v>
+        <v>1.7215577890025406</v>
       </c>
       <c r="C18">
         <v>511.37584442281513</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.3874719690188928</v>
+        <v>0.244190975799999</v>
       </c>
       <c r="B19">
-        <v>1.3874529914780209</v>
+        <v>1.0118814026439083</v>
       </c>
       <c r="C19">
         <v>511.37584442281513</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.2720310716423433</v>
+        <v>2.1304168948724351</v>
       </c>
       <c r="B20">
-        <v>0.66495205642932476</v>
+        <v>0.29375888631302466</v>
       </c>
       <c r="C20">
         <v>511.37584442281513</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.1531774399863091</v>
+        <v>4.0137735528561462</v>
       </c>
       <c r="B21">
-        <v>-0.066514138829466746</v>
+        <v>-0.43190765626889865</v>
       </c>
       <c r="C21">
         <v>511.37584442281513</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.03133442575878</v>
+        <v>5.8945429884440168</v>
       </c>
       <c r="B22">
-        <v>-0.80583344846114813</v>
+        <v>-1.1643766727519636</v>
       </c>
       <c r="C22">
         <v>511.37584442281513</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.9065587714563925</v>
+        <v>7.7727629867767094</v>
       </c>
       <c r="B23">
-        <v>-1.5528568098063682</v>
+        <v>-1.9035488162714875</v>
       </c>
       <c r="C23">
         <v>511.37584442281513</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>9.77881556727295</v>
+        <v>9.6484102696068437</v>
       </c>
       <c r="B24">
-        <v>-2.3076759310002433</v>
+        <v>-2.6494852913340976</v>
       </c>
       <c r="C24">
         <v>511.37584442281513</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>11.648069903402261</v>
+        <v>11.521461558687038</v>
       </c>
       <c r="B25">
-        <v>-3.0703825201778909</v>
+        <v>-3.402247302446419</v>
       </c>
       <c r="C25">
         <v>511.37584442281513</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>13.514271796309643</v>
+        <v>13.391883526800569</v>
       </c>
       <c r="B26">
-        <v>-3.8411078841911928</v>
+        <v>-4.1619224754431281</v>
       </c>
       <c r="C26">
         <v>511.37584442281513</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>15.377310967546528</v>
+        <v>15.259602650853378</v>
       </c>
       <c r="B27">
-        <v>-4.62014172475912</v>
+        <v>-4.9287041214711005</v>
       </c>
       <c r="C27">
         <v>511.37584442281513</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>17.237062064935838</v>
+        <v>17.124535358782037</v>
       </c>
       <c r="B28">
-        <v>-5.4078133423174</v>
+        <v>-5.7028119730052609</v>
       </c>
       <c r="C28">
         <v>511.37584442281513</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>19.093399736300519</v>
+        <v>18.986598078523151</v>
       </c>
       <c r="B29">
-        <v>-6.2044520373017695</v>
+        <v>-6.484465762520534</v>
       </c>
       <c r="C29">
         <v>511.37584442281513</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>20.94626697255346</v>
+        <v>20.845752758545348</v>
       </c>
       <c r="B30">
-        <v>-7.0102075727052862</v>
+        <v>-7.27376553729132</v>
       </c>
       <c r="C30">
         <v>511.37584442281513</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>22.795880136967408</v>
+        <v>22.702143429445471</v>
       </c>
       <c r="B31">
-        <v>-7.8245115617503069</v>
+        <v>-8.0703326037899288</v>
       </c>
       <c r="C31">
         <v>511.37584442281513</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>24.642523935905075</v>
+        <v>24.55595964235242</v>
       </c>
       <c r="B32">
-        <v>-8.64661608021652</v>
+        <v>-8.87366858328816</v>
       </c>
       <c r="C32">
         <v>511.37584442281513</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>26.486483075729165</v>
+        <v>26.40739094839509</v>
       </c>
       <c r="B33">
-        <v>-9.4757732038836124</v>
+        <v>-9.6832750970577948</v>
       </c>
       <c r="C33">
         <v>511.37584442281513</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>28.327931923850638</v>
+        <v>28.256553386899327</v>
       </c>
       <c r="B34">
-        <v>-10.311524869192121</v>
+        <v>-10.498847047830502</v>
       </c>
       <c r="C34">
         <v>511.37584442281513</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>30.166603491873563</v>
+        <v>30.103268949978759</v>
       </c>
       <c r="B35">
-        <v>-11.154572455226019</v>
+        <v>-11.320852464177444</v>
       </c>
       <c r="C35">
         <v>511.37584442281513</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>32.002120452450235</v>
+        <v>31.947286117943946</v>
       </c>
       <c r="B36">
-        <v>-12.005907201730114</v>
+        <v>-12.149952656129653</v>
       </c>
       <c r="C36">
         <v>511.37584442281513</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>33.834105478233013</v>
+        <v>33.788353371105522</v>
       </c>
       <c r="B37">
-        <v>-12.866520348449257</v>
+        <v>-12.986808933718184</v>
       </c>
       <c r="C37">
         <v>511.37584442281513</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>35.6619105876474</v>
+        <v>35.626038882035104</v>
       </c>
       <c r="B38">
-        <v>-13.738114144357624</v>
+        <v>-13.832556682449788</v>
       </c>
       <c r="C38">
         <v>511.37584442281513</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>37.483805182211768</v>
+        <v>37.459189592348714</v>
       </c>
       <c r="B39">
-        <v>-14.625234875346932</v>
+        <v>-14.690227589734166</v>
       </c>
       <c r="C39">
         <v>511.37584442281513</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>39.297788009217726</v>
+        <v>39.286472135923461</v>
       </c>
       <c r="B40">
-        <v>-15.533139836538259</v>
+        <v>-15.563327418456746</v>
       </c>
       <c r="C40">
         <v>511.37584442281513</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>41.101857815956841</v>
+        <v>41.106553146636436</v>
       </c>
       <c r="B41">
-        <v>-16.467086323052694</v>
+        <v>-16.455361931502942</v>
       </c>
       <c r="C41">
         <v>511.37584442281513</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>41.101857815956841</v>
+        <v>41.106553146636436</v>
       </c>
       <c r="B42">
-        <v>-16.467086323052694</v>
+        <v>-16.455361931502942</v>
       </c>
       <c r="C42">
         <v>511.37584442281513</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>39.203247870733968</v>
+        <v>39.223492606398992</v>
       </c>
       <c r="B43">
-        <v>-15.781496981394808</v>
+        <v>-15.728916819114311</v>
       </c>
       <c r="C43">
         <v>511.37584442281513</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>37.310961426332327</v>
+        <v>37.344046769404791</v>
       </c>
       <c r="B44">
-        <v>-15.079295789631265</v>
+        <v>-14.992967721095384</v>
       </c>
       <c r="C44">
         <v>511.37584442281513</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>35.422998415436517</v>
+        <v>35.466883454035631</v>
       </c>
       <c r="B45">
-        <v>-14.365736928853206</v>
+        <v>-14.251017285963666</v>
       </c>
       <c r="C45">
         <v>511.37584442281513</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>33.537358770731124</v>
+        <v>33.59067047867336</v>
       </c>
       <c r="B46">
-        <v>-13.646074580151776</v>
+        <v>-13.506568162236647</v>
       </c>
       <c r="C46">
         <v>511.37584442281513</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>31.652313038305387</v>
+        <v>31.714255928647155</v>
       </c>
       <c r="B47">
-        <v>-12.924852022628553</v>
+        <v>-12.762649030207545</v>
       </c>
       <c r="C47">
         <v>511.37584442281513</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>29.767214217867238</v>
+        <v>29.837208957075735</v>
       </c>
       <c r="B48">
-        <v>-12.203768927426935</v>
+        <v>-12.020392697272534</v>
       </c>
       <c r="C48">
         <v>511.37584442281513</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>27.881685922529169</v>
+        <v>27.959278984025115</v>
       </c>
       <c r="B49">
-        <v>-11.483814063700743</v>
+        <v>-11.280458002603494</v>
       </c>
       <c r="C49">
         <v>511.37584442281513</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>25.995351765403726</v>
+        <v>26.080215429561381</v>
       </c>
       <c r="B50">
-        <v>-10.765976200603809</v>
+        <v>-10.543503785372325</v>
       </c>
       <c r="C50">
         <v>511.37584442281513</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>24.107945652776969</v>
+        <v>24.199841179809731</v>
       </c>
       <c r="B51">
-        <v>-10.050954366888565</v>
+        <v>-9.8099957235635564</v>
       </c>
       <c r="C51">
         <v>511.37584442281513</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>22.219642663629042</v>
+        <v>22.318272985131948</v>
       </c>
       <c r="B52">
-        <v>-9.3382886297018377</v>
+        <v>-9.0796268504122448</v>
       </c>
       <c r="C52">
         <v>511.37584442281513</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>20.330728170113613</v>
+        <v>20.43570106194899</v>
       </c>
       <c r="B53">
-        <v>-8.6272293157890534</v>
+        <v>-8.3518970379660864</v>
       </c>
       <c r="C53">
         <v>511.37584442281513</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>18.441487544384337</v>
+        <v>18.552315626681771</v>
       </c>
       <c r="B54">
-        <v>-7.91702675189563</v>
+        <v>-7.62630615827277</v>
       </c>
       <c r="C54">
         <v>511.37584442281513</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>16.552137771157284</v>
+        <v>16.668261330904809</v>
       </c>
       <c r="B55">
-        <v>-7.2071109187109643</v>
+        <v>-6.9024738850944489</v>
       </c>
       <c r="C55">
         <v>511.37584442281513</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>14.66262228539823</v>
+        <v>14.783500566806833</v>
       </c>
       <c r="B56">
-        <v>-6.49763041270031</v>
+        <v>-6.1804990990511115</v>
       </c>
       <c r="C56">
         <v>511.37584442281513</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>12.772816134635336</v>
+        <v>12.897950161730158</v>
       </c>
       <c r="B57">
-        <v>-5.78891348427289</v>
+        <v>-5.4606004824772043</v>
       </c>
       <c r="C57">
         <v>511.37584442281513</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>10.882594366396791</v>
+        <v>11.011526943017094</v>
       </c>
       <c r="B58">
-        <v>-5.08128838383793</v>
+        <v>-4.7429967177071735</v>
       </c>
       <c r="C58">
         <v>511.37584442281513</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>8.9918470578217153</v>
+        <v>9.1241577428948144</v>
       </c>
       <c r="B59">
-        <v>-4.3750438789846928</v>
+        <v>-4.0278801816568075</v>
       </c>
       <c r="C59">
         <v>511.37584442281513</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>7.1005244044930844</v>
+        <v>7.235809413130025</v>
       </c>
       <c r="B60">
-        <v>-3.670310806022635</v>
+        <v>-3.3153380295672816</v>
       </c>
       <c r="C60">
         <v>511.37584442281513</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5.20859163160483</v>
+        <v>5.3464588103743091</v>
       </c>
       <c r="B61">
-        <v>-2.9671805184412596</v>
+        <v>-2.6054311112611148</v>
       </c>
       <c r="C61">
         <v>511.37584442281513</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3.3160139643508804</v>
+        <v>3.4560827912792464</v>
       </c>
       <c r="B62">
-        <v>-2.2657443697300677</v>
+        <v>-1.8982202765608263</v>
       </c>
       <c r="C62">
         <v>511.37584442281513</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.4228482343559488</v>
+        <v>1.5647192300467905</v>
       </c>
       <c r="B63">
-        <v>-1.5658530630900969</v>
+        <v>-1.1936059444367086</v>
       </c>
       <c r="C63">
         <v>511.37584442281513</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.47048230103217126</v>
+        <v>-0.32734992891966519</v>
       </c>
       <c r="B64">
-        <v>-0.86639470056850565</v>
+        <v>-0.49084681045013284</v>
       </c>
       <c r="C64">
         <v>511.37584442281513</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.3634627780348905</v>
+        <v>-2.2197817236663413</v>
       </c>
       <c r="B65">
-        <v>-0.16601673392399313</v>
+        <v>0.21095886068975148</v>
       </c>
       <c r="C65">
         <v>511.37584442281513</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.2555783328736263</v>
+        <v>-4.112233192239465</v>
       </c>
       <c r="B66">
-        <v>0.53663338508474323</v>
+        <v>0.91271280427379742</v>
       </c>
       <c r="C66">
         <v>511.37584442281513</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-6.1469792206738312</v>
+        <v>-6.0048044591511243</v>
       </c>
       <c r="B67">
-        <v>1.2411609359235949</v>
+        <v>1.614151767177177</v>
       </c>
       <c r="C67">
         <v>511.37584442281513</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-8.040476172177085</v>
+        <v>-7.8993679947768349</v>
       </c>
       <c r="B68">
-        <v>1.9401821229568006</v>
+        <v>2.3103525426123359</v>
       </c>
       <c r="C68">
         <v>511.37584442281513</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-9.9382461325463876</v>
+        <v>-9.7973740712433184</v>
       </c>
       <c r="B69">
-        <v>2.6279781066114389</v>
+        <v>2.9975019917059691</v>
       </c>
       <c r="C69">
         <v>511.37584442281513</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-11.837270429014236</v>
+        <v>-11.696811821818592</v>
       </c>
       <c r="B70">
-        <v>3.31247894666758</v>
+        <v>3.6808872009044675</v>
       </c>
       <c r="C70">
         <v>511.37584442281513</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-13.734257862065752</v>
+        <v>-13.595488838103409</v>
       </c>
       <c r="B71">
-        <v>4.0023306312502589</v>
+        <v>4.3662725764454109</v>
       </c>
       <c r="C71">
         <v>511.37584442281513</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-15.630022743127011</v>
+        <v>-15.493947683888004</v>
       </c>
       <c r="B72">
-        <v>4.6953939625113623</v>
+        <v>5.0522315784114005</v>
       </c>
       <c r="C72">
         <v>511.37584442281513</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-17.525925633180037</v>
+        <v>-17.393094824067607</v>
       </c>
       <c r="B73">
-        <v>5.3880947438575761</v>
+        <v>5.7363808771737217</v>
       </c>
       <c r="C73">
         <v>511.37584442281513</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-19.421406580489705</v>
+        <v>-19.292557355767883</v>
       </c>
       <c r="B74">
-        <v>6.08190396968794</v>
+        <v>6.4197009304133594</v>
       </c>
       <c r="C74">
         <v>511.37584442281513</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-21.315414991472863</v>
+        <v>-21.191635534019895</v>
       </c>
       <c r="B75">
-        <v>6.7795815515797155</v>
+        <v>7.1040315478413474</v>
       </c>
       <c r="C75">
         <v>511.37584442281513</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-23.206858217871392</v>
+        <v>-23.089601613246064</v>
       </c>
       <c r="B76">
-        <v>7.4839978788307295</v>
+        <v>7.79128615997925</v>
       </c>
       <c r="C76">
         <v>511.37584442281513</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-25.094724530731845</v>
+        <v>-24.98578176120634</v>
       </c>
       <c r="B77">
-        <v>8.1978107655533243</v>
+        <v>8.48323644530124</v>
       </c>
       <c r="C77">
         <v>511.37584442281513</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-26.978367932994477</v>
+        <v>-26.879745799619595</v>
       </c>
       <c r="B78">
-        <v>8.922717247397328</v>
+        <v>9.1810134532814356</v>
       </c>
       <c r="C78">
         <v>511.37584442281513</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-28.85668786514751</v>
+        <v>-28.770760742614545</v>
       </c>
       <c r="B79">
-        <v>9.6616084965407314</v>
+        <v>9.8865443925228682</v>
       </c>
       <c r="C79">
         <v>511.37584442281513</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-30.727754214568108</v>
+        <v>-30.657540997117142</v>
       </c>
       <c r="B80">
-        <v>10.419554922948528</v>
+        <v>10.603209418263756</v>
       </c>
       <c r="C80">
         <v>511.37584442281513</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-32.586828580518542</v>
+        <v>-32.536930191517868</v>
       </c>
       <c r="B81">
-        <v>11.209004315435951</v>
+        <v>11.3393074442467</v>
       </c>
       <c r="C81">
         <v>511.37584442281513</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-34.3486098284991</v>
+        <v>-34.352103723059315</v>
       </c>
       <c r="B82">
-        <v>12.254042935744762</v>
+        <v>12.244244983734808</v>
       </c>
       <c r="C82">
         <v>511.37584442281513</v>
